--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5310-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5310-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEB5FB31-F803-4249-BC51-8E9D7857819D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79975AB0-D18C-403E-961F-D6517E23C575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{AA919555-8447-4131-BD7E-E80CFB167D73}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{19BB1B32-E244-4F17-BCA1-B8F1C3A090B7}"/>
   </bookViews>
   <sheets>
     <sheet name="5310-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1454,28 +1454,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B862C7-A836-45BD-BA21-2FCD0CCDC7E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8F1351-B4FC-4DFB-A251-1F55E5F2ACE6}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1508,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1545,7 +1544,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1597,7 +1596,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1665,7 +1664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1737,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1809,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1881,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2025,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2241,7 +2240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2457,7 +2456,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2529,7 +2528,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2601,7 +2600,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2673,7 +2672,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3249,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3465,7 +3464,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1998</v>
       </c>
@@ -3609,7 +3608,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1997</v>
       </c>
@@ -3681,7 +3680,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1996</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1995</v>
       </c>
@@ -3825,7 +3824,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>1994</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1993</v>
       </c>
@@ -3969,7 +3968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>1992</v>
       </c>
@@ -4041,7 +4040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>44</v>
       </c>
